--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18216,7 +18216,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21432,7 +21432,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23442,7 +23442,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23844,7 +23844,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25050,7 +25050,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27864,7 +27864,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28266,7 +28266,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28668,7 +28668,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29070,7 +29070,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30678,7 +30678,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31482,7 +31482,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31884,7 +31884,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -32286,7 +32286,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32688,7 +32688,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33492,7 +33492,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34698,7 +34698,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35100,7 +35100,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35904,7 +35904,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -36306,7 +36306,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36708,7 +36708,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -37110,7 +37110,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -37512,7 +37512,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37914,7 +37914,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38316,7 +38316,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -39120,7 +39120,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -39522,7 +39522,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40326,7 +40326,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40728,7 +40728,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -41130,7 +41130,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41934,7 +41934,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42738,7 +42738,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -43542,7 +43542,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43944,7 +43944,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -45150,7 +45150,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -45552,7 +45552,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45954,7 +45954,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -46356,7 +46356,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46758,7 +46758,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -47160,7 +47160,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47562,7 +47562,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47964,7 +47964,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -48366,7 +48366,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -48768,7 +48768,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -49170,7 +49170,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -49572,7 +49572,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49974,7 +49974,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -50376,7 +50376,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -50778,7 +50778,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -51180,7 +51180,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -51582,7 +51582,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">

--- a/diseases/d224/2010-2014.xlsx
+++ b/diseases/d224/2010-2014.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25442,7 +25442,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31472,7 +31472,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32678,7 +32678,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35492,7 +35492,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36698,7 +36698,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37502,7 +37502,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37904,7 +37904,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48356,7 +48356,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -49160,7 +49160,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49964,7 +49964,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50768,7 +50768,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -51170,7 +51170,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
